--- a/docs/bloodline_data.xlsx
+++ b/docs/bloodline_data.xlsx
@@ -945,7 +945,7 @@
         <v>33</v>
       </c>
       <c r="E2">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -962,7 +962,7 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -979,7 +979,7 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/docs/bloodline_data.xlsx
+++ b/docs/bloodline_data.xlsx
@@ -395,31 +395,31 @@
     <t>en</t>
   </si>
   <si>
-    <t>Hacía los mejores ñoquis del barrio.</t>
-  </si>
-  <si>
-    <t>Ganó un concurso de tango en 1923.</t>
-  </si>
-  <si>
-    <t>Nunca perdió un truco en su vida.</t>
-  </si>
-  <si>
-    <t>Cruzó el Atlántico en barco con una valija y un salame.</t>
-  </si>
-  <si>
-    <t>Tenía un loro que sabía el himno.</t>
-  </si>
-  <si>
-    <t>Atendía el almacén y fiaba a medio pueblo.</t>
+    <t>Hacía los mejores ñoquis de todo el barrio.</t>
+  </si>
+  <si>
+    <t>Ganó un concurso de tango en el club en 1923.</t>
+  </si>
+  <si>
+    <t>Nunca en su vida perdió una partida de truco.</t>
+  </si>
+  <si>
+    <t>Cruzó el Atlántico con una valija y un salame.</t>
+  </si>
+  <si>
+    <t>Tenía un loro que cantaba el himno completo.</t>
+  </si>
+  <si>
+    <t>Atendía el almacén y le fiaba a medio pueblo.</t>
   </si>
   <si>
     <t>Tocaba el bandoneón en todos los casamientos.</t>
   </si>
   <si>
-    <t>Escribía cartas de amor por encargo.</t>
-  </si>
-  <si>
-    <t>Domaba caballos los domingos.</t>
+    <t>Escribía cartas de amor por encargo en el pueblo.</t>
+  </si>
+  <si>
+    <t>Domaba caballos salvajes todos los domingos.</t>
   </si>
   <si>
     <t>Fue la primera persona del pueblo en tener radio.</t>
@@ -428,67 +428,67 @@
     <t>Juraba haber visto un plato volador en 1911.</t>
   </si>
   <si>
-    <t>Cocinaba un locro que se olía desde la estación.</t>
-  </si>
-  <si>
-    <t>Coleccionaba botones de uniformes.</t>
-  </si>
-  <si>
-    <t>Le ganó una pulseada al comisario.</t>
+    <t>Su locro se olía desde la estación de tren.</t>
+  </si>
+  <si>
+    <t>Coleccionaba botones de uniformes militares.</t>
+  </si>
+  <si>
+    <t>Le ganó una pulseada al comisario del pueblo.</t>
   </si>
   <si>
     <t>Plantó el ombú que todavía está en la plaza.</t>
   </si>
   <si>
-    <t>Sabía leer las nubes y nunca le erró al pronóstico.</t>
-  </si>
-  <si>
-    <t>Made the best gnocchi in the neighbourhood.</t>
-  </si>
-  <si>
-    <t>Won a tango contest in 1923.</t>
-  </si>
-  <si>
-    <t>Never lost a game of truco in their life.</t>
-  </si>
-  <si>
-    <t>Crossed the Atlantic with one suitcase and a salami.</t>
-  </si>
-  <si>
-    <t>Had a parrot that knew the national anthem.</t>
-  </si>
-  <si>
-    <t>Ran the grocery store and gave credit to half the town.</t>
-  </si>
-  <si>
-    <t>Played the bandoneon at every wedding.</t>
-  </si>
-  <si>
-    <t>Wrote love letters for hire.</t>
-  </si>
-  <si>
-    <t>Tamed horses on Sundays.</t>
-  </si>
-  <si>
-    <t>First person in town to own a radio.</t>
-  </si>
-  <si>
-    <t>Swore they saw a flying saucer in 1911.</t>
-  </si>
-  <si>
-    <t>Cooked a stew you could smell from the train station.</t>
-  </si>
-  <si>
-    <t>Collected uniform buttons.</t>
-  </si>
-  <si>
-    <t>Beat the police chief at arm wrestling.</t>
+    <t>Leía las nubes y nunca le erró al pronóstico.</t>
+  </si>
+  <si>
+    <t>Made the best gnocchi in the whole neighbourhood.</t>
+  </si>
+  <si>
+    <t>Won the club's tango contest back in 1923.</t>
+  </si>
+  <si>
+    <t>Never lost a single game of truco in their life.</t>
+  </si>
+  <si>
+    <t>Crossed the Atlantic with a suitcase and a salami.</t>
+  </si>
+  <si>
+    <t>Had a parrot that could sing the whole anthem.</t>
+  </si>
+  <si>
+    <t>Ran the store and gave credit to half the town.</t>
+  </si>
+  <si>
+    <t>Played the bandoneon at every single wedding.</t>
+  </si>
+  <si>
+    <t>Wrote love letters for hire for the whole town.</t>
+  </si>
+  <si>
+    <t>Spent every Sunday taming wild horses on the farm.</t>
+  </si>
+  <si>
+    <t>Was the first person in town to own a radio.</t>
+  </si>
+  <si>
+    <t>Swore they saw a flying saucer back in 1911.</t>
+  </si>
+  <si>
+    <t>Their stew could be smelled from the train station.</t>
+  </si>
+  <si>
+    <t>Collected buttons from old military uniforms.</t>
+  </si>
+  <si>
+    <t>Beat the town's police chief at arm wrestling.</t>
   </si>
   <si>
     <t>Planted the ombú tree still standing in the square.</t>
   </si>
   <si>
-    <t>Could read the clouds and never got the weather wrong.</t>
+    <t>Read the clouds and never got the weather wrong.</t>
   </si>
 </sst>
 </file>
@@ -945,7 +945,7 @@
         <v>33</v>
       </c>
       <c r="E2">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -962,7 +962,7 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -979,7 +979,7 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/docs/bloodline_data.xlsx
+++ b/docs/bloodline_data.xlsx
@@ -101,13 +101,13 @@
     <t>cosmetic</t>
   </si>
   <si>
-    <t>Enfermedad 1</t>
-  </si>
-  <si>
-    <t>Enfermedad 2</t>
-  </si>
-  <si>
-    <t>Enfermedad 3</t>
+    <t>Tos de Quilmes</t>
+  </si>
+  <si>
+    <t>Fiebre del Bandoneón</t>
+  </si>
+  <si>
+    <t>Síndrome del Mate Frío</t>
   </si>
   <si>
     <t>Color de ojos</t>
@@ -119,13 +119,13 @@
     <t>Pecas</t>
   </si>
   <si>
-    <t>Disease 1</t>
-  </si>
-  <si>
-    <t>Disease 2</t>
-  </si>
-  <si>
-    <t>Disease 3</t>
+    <t>Quilmes Cough</t>
+  </si>
+  <si>
+    <t>Bandoneon Fever</t>
+  </si>
+  <si>
+    <t>Cold Mate Syndrome</t>
   </si>
   <si>
     <t>Eye colour</t>
